--- a/output/pdf_financials_xlsx/MCS.xlsx
+++ b/output/pdf_financials_xlsx/MCS.xlsx
@@ -5325,7 +5325,7 @@
         <v>-0.330858</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>1.234536</v>
+        <v>-1.234536</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-0.374537</v>
@@ -17529,7 +17529,7 @@
         </is>
       </c>
       <c r="N126" s="5" t="n">
-        <v>1.234536</v>
+        <v>-1.234536</v>
       </c>
       <c r="O126" s="5" t="n">
         <v>-0.374537</v>

--- a/output/pdf_financials_xlsx/MCS.xlsx
+++ b/output/pdf_financials_xlsx/MCS.xlsx
@@ -2114,43 +2114,43 @@
         <v>0.112545</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.128956</v>
+        <v>0.6465070000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.168353</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.143491</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.19969</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.154277</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.157966</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.659789</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.602653</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.523432</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.915057</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.471805</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.43485</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>5.146047</v>
       </c>
     </row>
     <row r="35">
@@ -2212,43 +2212,43 @@
         <v>1.298471</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>6.382616</v>
+        <v>6.900167</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>6.80442</v>
+        <v>6.972773</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.959276</v>
+        <v>1.102767</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.848932</v>
+        <v>1.048622</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.845141</v>
+        <v>0.999418</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.14708</v>
+        <v>2.305046</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.028373</v>
+        <v>4.688162</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>3.521889</v>
+        <v>4.124542</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>7.258946</v>
+        <v>7.782378</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>7.368224</v>
+        <v>8.283281000000001</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>8.372296</v>
+        <v>8.844101</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>10.395501</v>
+        <v>10.830351</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>6.544545</v>
+        <v>11.690592</v>
       </c>
     </row>
     <row r="37">
@@ -2800,43 +2800,43 @@
         <v>0.304882</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.853311</v>
+        <v>0.33576</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.587774</v>
+        <v>0.419421</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.143491</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.19969</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.154277</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.157966</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.659789</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.886871</v>
+        <v>0.284218</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.495132</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.915057</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.471805</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.43485</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>5.396047</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="49">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/MCS.xlsx
+++ b/output/pdf_financials_xlsx/MCS.xlsx
@@ -6033,46 +6033,46 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-1.336936</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-11.910323</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-7.727508</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-1.088574</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-0.525102</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-0.237504</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.393041</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-1.092302</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-3.228669</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-0.856692</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-5.68205</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-2.10374</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0</v>
+        <v>-0.567439</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0</v>
+        <v>-0.06307</v>
       </c>
     </row>
     <row r="115">
@@ -14286,7 +14286,11 @@
           <t>Purchase of marketable securities (Note 3, 6, 8, 9)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -16144,7 +16148,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="n">
         <v>5.538272</v>
       </c>
@@ -16220,7 +16228,11 @@
           <t>Deferred income taxes expense</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -19524,7 +19536,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E150" s="5" t="n">
         <v>-1.336936</v>
       </c>
@@ -21978,7 +21994,11 @@
           <t>Deferred income taxes recovery</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -22404,7 +22424,11 @@
           <t>Deferred income taxes (recovery)</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E185" s="5" t="n">
         <v>0.620216</v>
       </c>
